--- a/config/unknowable-domain-generated/templates/UnknowableDomainBindings.xlsx
+++ b/config/unknowable-domain-generated/templates/UnknowableDomainBindings.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2164" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2161" uniqueCount="193">
   <si>
     <t>@table</t>
   </si>
@@ -295,7 +295,7 @@
     <t>UnknowableDomainCurioRule</t>
   </si>
   <si>
-    <t>6c0f0a9c3bf1a0f7</t>
+    <t>9e8b831d9a3de344</t>
   </si>
   <si>
     <t>curio_group_id</t>
@@ -7214,8 +7214,7 @@
     <col min="18" max="18" width="12.7109375" style="5" customWidth="1"/>
     <col min="19" max="19" width="14.7109375" style="5" customWidth="1"/>
     <col min="20" max="20" width="12.7109375" style="5" customWidth="1"/>
-    <col min="21" max="21" width="16.7109375" style="5" customWidth="1"/>
-    <col min="22" max="24" width="12.7109375" style="5" customWidth="1"/>
+    <col min="21" max="24" width="16.7109375" style="5" customWidth="1"/>
     <col min="25" max="25" width="15.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7470,13 +7469,13 @@
         <v>29</v>
       </c>
       <c r="V4" s="5" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="W4" s="5" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="X4" s="5" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="Y4" s="5" t="s">
         <v>64</v>
@@ -7613,15 +7612,9 @@
       <c r="U6" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="V6" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="W6" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="X6" s="5" t="s">
-        <v>53</v>
-      </c>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="5"/>
       <c r="Y6" s="5"/>
     </row>
     <row r="7" spans="1:25" ht="42" customHeight="1">

--- a/config/unknowable-domain-generated/templates/UnknowableDomainBindings.xlsx
+++ b/config/unknowable-domain-generated/templates/UnknowableDomainBindings.xlsx
@@ -1756,7 +1756,7 @@
         <v>54</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="U6" s="5" t="s">
         <v>53</v>
@@ -3036,7 +3036,7 @@
         <v>37</v>
       </c>
       <c r="R6" s="5" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="S6" s="5" t="s">
         <v>53</v>
